--- a/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11790" windowHeight="10800" activeTab="2"/>
+    <workbookView windowWidth="11640" windowHeight="8715"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="75">
   <si>
     <t>名称</t>
   </si>
@@ -45,187 +45,187 @@
     <t>圣殿斥候</t>
   </si>
   <si>
+    <t>圣殿弩手</t>
+  </si>
+  <si>
+    <t>田园守望者</t>
+  </si>
+  <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>炽阳坠落</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>心灵黑洞</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>黑金勒索者</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>海燕精卫</t>
+  </si>
+  <si>
+    <t>海盗船长</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>花剑绅士·翔</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>钢之咆哮·布瑞恩</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>万圣节草人</t>
+  </si>
+  <si>
+    <t>沉重否定</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>占卜命运</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>飓风术</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>泰山之力</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
     <t>圣殿卫士</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>炽阳坠落</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>帝国军魂·莱哈特</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>心灵黑洞</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>黑金勒索者</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>海燕精卫</t>
-  </si>
-  <si>
-    <t>海盗船长</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>钢之咆哮·布瑞恩</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>占卜命运</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>飓风术</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>泰山之力</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
   </si>
   <si>
     <t>蒙面侠客·翔</t>
@@ -1229,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1237,7 +1237,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1259,18 +1259,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1281,52 +1281,52 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>21.5</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>21.6</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1334,32 +1334,32 @@
         <v>1</v>
       </c>
       <c r="C12" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
@@ -1370,12 +1370,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1389,19 +1389,13 @@
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4</v>
-      </c>
-      <c r="C18" s="2">
-        <v>20</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1409,20 +1403,26 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C11:C17)</f>
+        <v>21.7142857142857</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C12:C18)</f>
-        <v>21.4285714285714</v>
+      <c r="B23" s="4">
+        <v>3</v>
+      </c>
+      <c r="C23" s="4">
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1430,10 +1430,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1444,7 +1444,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1452,10 +1452,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1463,7 +1463,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="4">
         <v>21</v>
@@ -1474,22 +1474,16 @@
         <v>22</v>
       </c>
       <c r="B28" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="4">
-        <v>8</v>
-      </c>
-      <c r="C29" s="4">
-        <v>20</v>
-      </c>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="4"/>
@@ -1497,39 +1491,34 @@
       <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="4" t="s">
+      <c r="A31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="4">
+        <f>AVERAGE(C23:C28)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C24:C29)</f>
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="5">
-        <f>AVERAGE(C2:C6,C12:C18,C24:C29)</f>
-        <v>21.1666666666667</v>
+      <c r="C34" s="5">
+        <f>AVERAGE(C2:C5,C11:C17,C23:C28)</f>
+        <v>21.4117647058824</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C9 C35" formulaRange="1"/>
+    <ignoredError sqref="C34 C8" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1545,7 +1534,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1556,9 +1545,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1567,20 +1556,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1589,31 +1578,31 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1622,9 +1611,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1633,43 +1622,43 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>19.25</v>
+        <v>20.125</v>
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -1678,20 +1667,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -1712,30 +1701,30 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C15:C17)</f>
-        <v>19.3333333333333</v>
+        <v>19.6666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="4">
         <v>2</v>
       </c>
       <c r="C23" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="4">
         <v>3</v>
@@ -1746,24 +1735,24 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="4">
         <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1778,26 +1767,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C23:C26)</f>
-        <v>18</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
-        <v>18.9333333333333</v>
+        <v>19.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1806,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1828,9 +1817,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1839,20 +1828,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1861,20 +1850,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1883,9 +1872,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1894,32 +1883,32 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -1928,9 +1917,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -1939,42 +1928,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -1985,7 +1974,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1996,7 +1985,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -2017,25 +2006,25 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C13:C20)</f>
-        <v>16.25</v>
+        <v>16.875</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2050,26 +2039,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C7,C13:C20,C26:C26)</f>
-        <v>16.5333333333333</v>
+        <v>16.7333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +2078,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2100,9 +2089,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2111,9 +2100,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2122,9 +2111,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2133,9 +2122,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -2144,9 +2133,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2155,9 +2144,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2166,9 +2155,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2177,9 +2166,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2188,9 +2177,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2199,9 +2188,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
@@ -2210,9 +2199,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
@@ -2221,9 +2210,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1">
         <v>4</v>
@@ -2232,22 +2221,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C16" s="1">
         <f>AVERAGE(C2:C13)</f>
@@ -2257,7 +2246,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2268,7 +2257,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="2">
         <v>4</v>
@@ -2289,10 +2278,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C19:C20)</f>
@@ -2301,7 +2290,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="4">
         <v>4</v>
@@ -2322,10 +2311,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
@@ -2334,10 +2323,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C13,C19:C20,C26:C26)</f>
@@ -2385,7 +2374,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -2396,7 +2385,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -2407,7 +2396,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2418,7 +2407,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2429,7 +2418,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -2440,7 +2429,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2451,7 +2440,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2462,7 +2451,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2473,7 +2462,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -2484,7 +2473,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="1">
         <v>5</v>
@@ -2505,19 +2494,19 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C15" s="1">
         <f>AVERAGE(C2:C12)</f>
         <v>20.5454545454545</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -2526,9 +2515,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -2537,9 +2526,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -2548,9 +2537,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -2559,9 +2548,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2">
         <v>3</v>
@@ -2570,9 +2559,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2">
         <v>3</v>
@@ -2581,9 +2570,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2">
         <v>4</v>
@@ -2592,9 +2581,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2">
         <v>4</v>
@@ -2605,7 +2594,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2">
         <v>4</v>
@@ -2615,29 +2604,29 @@
       </c>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2">
         <f>AVERAGE(C18:C26)</f>
         <v>20.8888888888889</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
         <v>65</v>
       </c>
@@ -2694,7 +2683,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="4">
         <v>4</v>
@@ -2759,10 +2748,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" s="4">
         <f>AVERAGE(C32:C41)</f>
@@ -2771,7 +2760,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>74</v>

--- a/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11640" windowHeight="8715"/>
+    <workbookView windowWidth="9105" windowHeight="11040" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="76">
   <si>
     <t>名称</t>
   </si>
@@ -111,7 +111,10 @@
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>心灵黑洞</t>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
   </si>
   <si>
     <t>狡诈学徒</t>
@@ -135,9 +138,6 @@
     <t>海燕精卫</t>
   </si>
   <si>
-    <t>海盗船长</t>
-  </si>
-  <si>
     <t>黑金诈术师</t>
   </si>
   <si>
@@ -150,27 +150,30 @@
     <t>赤影·艾希尔</t>
   </si>
   <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
     <t>钢之咆哮·布瑞恩</t>
   </si>
   <si>
     <t>港口卡等：</t>
   </si>
   <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>万圣节草人</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
+    <t>学仆-观测型1</t>
+  </si>
+  <si>
+    <t>学仆-观测型2</t>
+  </si>
+  <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
   </si>
   <si>
     <t>全数否定</t>
   </si>
   <si>
-    <t>占卜命运</t>
-  </si>
-  <si>
     <t>隐形术</t>
   </si>
   <si>
@@ -180,7 +183,10 @@
     <t>克隆术</t>
   </si>
   <si>
-    <t>学仆-脉冲型</t>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
   </si>
   <si>
     <t>幻域秘树</t>
@@ -223,9 +229,6 @@
   </si>
   <si>
     <t>禅意卡等：</t>
-  </si>
-  <si>
-    <t>圣殿卫士</t>
   </si>
   <si>
     <t>蒙面侠客·翔</t>
@@ -268,7 +271,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +303,13 @@
     <font>
       <sz val="11"/>
       <color theme="5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -769,137 +779,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -916,6 +926,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1235,6 +1248,7 @@
     <col min="1" max="1" width="16.375" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1422,7 +1436,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1444,7 +1458,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1466,7 +1480,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1518,7 +1532,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C34 C8" formulaRange="1"/>
+    <ignoredError sqref="C8 C34" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1553,12 +1567,12 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -1569,7 +1583,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1580,7 +1594,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1591,18 +1605,18 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1613,7 +1627,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1624,7 +1638,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -1652,13 +1666,13 @@
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>20.125</v>
+        <v>20.375</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -1669,25 +1683,19 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>17</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1695,39 +1703,45 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C15:C17)</f>
-        <v>19.6666666666667</v>
+      <c r="C19" s="2">
+        <f>AVERAGE(C15:C16)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2</v>
+      </c>
+      <c r="C22" s="4">
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="4">
         <v>18</v>
@@ -1735,18 +1749,18 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="4">
         <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
@@ -1773,8 +1787,8 @@
         <v>23</v>
       </c>
       <c r="C29" s="4">
-        <f>AVERAGE(C23:C26)</f>
-        <v>18.75</v>
+        <f>AVERAGE(C22:C26)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1782,11 +1796,11 @@
         <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C32" s="5">
-        <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
-        <v>19.6666666666667</v>
+        <f>AVERAGE(C2:C9,C15:C16,C22:C26)</f>
+        <v>19.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1819,7 +1833,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1830,29 +1844,29 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1863,7 +1877,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1873,15 +1887,9 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>12</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1"/>
@@ -1889,70 +1897,76 @@
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>16.5</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>18</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -1963,18 +1977,18 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1985,13 +1999,13 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
       </c>
       <c r="C20" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2012,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="C23" s="2">
-        <f>AVERAGE(C13:C20)</f>
-        <v>16.875</v>
+        <f>AVERAGE(C12:C20)</f>
+        <v>17.1111111111111</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
@@ -2054,11 +2068,11 @@
         <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C32" s="5">
-        <f>AVERAGE(C2:C7,C13:C20,C26:C26)</f>
-        <v>16.7333333333333</v>
+        <f>AVERAGE(C2:C6,C12:C20,C26:C26)</f>
+        <v>17.4</v>
       </c>
     </row>
   </sheetData>
@@ -2091,7 +2105,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2102,7 +2116,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2113,7 +2127,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2124,7 +2138,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -2135,7 +2149,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2146,7 +2160,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2157,7 +2171,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2168,7 +2182,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2179,7 +2193,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2190,7 +2204,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
@@ -2201,7 +2215,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
@@ -2212,7 +2226,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B13" s="1">
         <v>4</v>
@@ -2246,7 +2260,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2257,7 +2271,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2">
         <v>4</v>
@@ -2290,7 +2304,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B26" s="4">
         <v>4</v>
@@ -2326,7 +2340,7 @@
         <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C13,C19:C20,C26:C26)</f>
@@ -2380,23 +2394,23 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2407,7 +2421,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2418,13 +2432,13 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2440,7 +2454,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2451,7 +2465,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2468,7 +2482,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2501,7 +2515,7 @@
       </c>
       <c r="C15" s="1">
         <f>AVERAGE(C2:C12)</f>
-        <v>20.5454545454545</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2512,7 +2526,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2523,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2539,7 +2553,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -2589,7 +2603,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2600,7 +2614,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E26" s="3"/>
     </row>
@@ -2623,45 +2637,45 @@
       </c>
       <c r="C29" s="2">
         <f>AVERAGE(C18:C26)</f>
-        <v>20.8888888888889</v>
+        <v>21.3333333333333</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B32" s="4">
         <v>2</v>
       </c>
       <c r="C32" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" s="4">
         <v>3</v>
       </c>
       <c r="C33" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B34" s="4">
         <v>3</v>
       </c>
       <c r="C34" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B35" s="4">
         <v>4</v>
@@ -2672,7 +2686,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B36" s="4">
         <v>4</v>
@@ -2689,45 +2703,45 @@
         <v>4</v>
       </c>
       <c r="C37" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B38" s="4">
         <v>5</v>
       </c>
       <c r="C38" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B39" s="4">
         <v>5</v>
       </c>
       <c r="C39" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B40" s="4">
         <v>6</v>
       </c>
       <c r="C40" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B41" s="4">
         <v>8</v>
@@ -2755,7 +2769,7 @@
       </c>
       <c r="C44" s="4">
         <f>AVERAGE(C32:C41)</f>
-        <v>19.4</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2763,11 +2777,11 @@
         <v>24</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C47" s="5">
         <f>AVERAGE(C2:C12,C18:C26,C32:C41)</f>
-        <v>20.2666666666667</v>
+        <v>20.8666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9105" windowHeight="11040" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="11910" windowHeight="11745" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="76">
   <si>
     <t>名称</t>
   </si>
@@ -63,172 +63,172 @@
     <t>四芒军旗</t>
   </si>
   <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>炽阳坠落</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>黑金勒索者</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>海燕精卫</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>花剑绅士·翔</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
+    <t>钢之咆哮·布瑞恩</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
+    <t>学仆-观测型1</t>
+  </si>
+  <si>
+    <t>学仆-观测型2</t>
+  </si>
+  <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>飓风术</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>泰山之力</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
     <t>传记·钢铁守卫</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>炽阳坠落</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>帝国军魂·莱哈特</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>心灵黑洞1</t>
-  </si>
-  <si>
-    <t>心灵黑洞2</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>黑金勒索者</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>海燕精卫</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>魔卡幻术师·梅基</t>
-  </si>
-  <si>
-    <t>钢之咆哮·布瑞恩</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型1</t>
-  </si>
-  <si>
-    <t>学仆-观测型2</t>
-  </si>
-  <si>
-    <t>沉重否定1</t>
-  </si>
-  <si>
-    <t>沉重否定2</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型2</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>飓风术</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>泰山之力</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
   </si>
   <si>
     <t>蒙面侠客·翔</t>
@@ -1242,7 +1242,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1345,7 +1345,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
         <v>22</v>
@@ -1356,7 +1356,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
         <v>22</v>
@@ -1378,7 +1378,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
         <v>22</v>
@@ -1392,19 +1392,13 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>20</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1412,20 +1406,26 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
+        <f>AVERAGE(C11:C16)</f>
+        <v>21.6666666666667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>21.7142857142857</v>
+      <c r="B22" s="4">
+        <v>3</v>
+      </c>
+      <c r="C22" s="4">
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1433,7 +1433,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="4">
         <v>22</v>
@@ -1447,7 +1447,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="4">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1455,10 +1455,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="4">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1466,7 +1466,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="4">
         <v>22</v>
@@ -1477,22 +1477,16 @@
         <v>21</v>
       </c>
       <c r="B27" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="4">
-        <v>8</v>
-      </c>
-      <c r="C28" s="4">
-        <v>20</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4"/>
@@ -1500,39 +1494,34 @@
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
+      <c r="A30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="4">
+        <f>AVERAGE(C22:C27)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="4">
-        <f>AVERAGE(C23:C28)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" s="5">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C28)</f>
-        <v>21.4117647058824</v>
+      <c r="C33" s="5">
+        <f>AVERAGE(C2:C5,C11:C16,C22:C27)</f>
+        <v>21.375</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C8 C34" formulaRange="1"/>
+    <ignoredError sqref="C33 C8" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1561,7 +1550,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1572,18 +1561,18 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1594,7 +1583,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1605,7 +1594,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1616,7 +1605,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1627,7 +1616,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1638,13 +1627,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1666,13 +1655,13 @@
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>20.375</v>
+        <v>20.625</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -1683,7 +1672,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
@@ -1707,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="2">
         <f>AVERAGE(C15:C16)</f>
@@ -1716,18 +1705,18 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="4">
         <v>2</v>
       </c>
       <c r="C22" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="4">
         <v>3</v>
@@ -1738,7 +1727,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="4">
         <v>4</v>
@@ -1749,18 +1738,18 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="4">
         <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
@@ -1784,23 +1773,23 @@
         <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C22:C26)</f>
-        <v>18</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C9,C15:C16,C22:C26)</f>
-        <v>19.5333333333333</v>
+        <v>19.8</v>
       </c>
     </row>
   </sheetData>
@@ -1833,7 +1822,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1844,18 +1833,18 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1866,7 +1855,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1877,7 +1866,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1905,13 +1894,13 @@
       </c>
       <c r="C9" s="1">
         <f>AVERAGE(C2:C6)</f>
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2">
         <v>1</v>
@@ -1922,7 +1911,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1933,7 +1922,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -1944,7 +1933,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -1955,18 +1944,18 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -1977,7 +1966,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -1988,7 +1977,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1999,7 +1988,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -2023,16 +2012,16 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C12:C20)</f>
-        <v>17.1111111111111</v>
+        <v>17.2222222222222</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
@@ -2056,7 +2045,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
@@ -2065,14 +2054,14 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C6,C12:C20,C26:C26)</f>
-        <v>17.4</v>
+        <v>17.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2094,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2116,7 +2105,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2127,7 +2116,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2138,7 +2127,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -2149,7 +2138,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2160,7 +2149,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2171,7 +2160,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2182,7 +2171,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2193,7 +2182,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2204,7 +2193,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
@@ -2215,7 +2204,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
@@ -2226,7 +2215,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1">
         <v>4</v>
@@ -2260,7 +2249,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2271,7 +2260,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2">
         <v>4</v>
@@ -2295,7 +2284,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C19:C20)</f>
@@ -2304,7 +2293,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B26" s="4">
         <v>4</v>
@@ -2328,7 +2317,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
@@ -2337,10 +2326,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C13,C19:C20,C26:C26)</f>
@@ -2388,7 +2377,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -2399,7 +2388,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -2410,7 +2399,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2421,7 +2410,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2432,7 +2421,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -2454,7 +2443,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2465,7 +2454,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2531,7 +2520,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -2542,7 +2531,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -2553,7 +2542,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -2564,7 +2553,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="2">
         <v>3</v>
@@ -2575,7 +2564,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="2">
         <v>3</v>
@@ -2586,7 +2575,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2">
         <v>4</v>
@@ -2597,7 +2586,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="2">
         <v>4</v>
@@ -2608,7 +2597,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2">
         <v>4</v>
@@ -2633,7 +2622,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="2">
         <f>AVERAGE(C18:C26)</f>
@@ -2697,7 +2686,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="4">
         <v>4</v>
@@ -2765,7 +2754,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C44" s="4">
         <f>AVERAGE(C32:C41)</f>
@@ -2774,7 +2763,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>75</v>

--- a/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/xingkongCard/z_level.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\views\game\zlzq\cardList\xingkongCard\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11910" windowHeight="11745" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="11985" windowHeight="9795" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="77">
   <si>
     <t>名称</t>
   </si>
@@ -45,190 +50,193 @@
     <t>圣殿斥候</t>
   </si>
   <si>
+    <t>田园守望者</t>
+  </si>
+  <si>
+    <t>塔楼弓手</t>
+  </si>
+  <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>炽阳坠落</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>帝国军魂·莱哈特</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>黑金勒索者</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>海燕精卫</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>花剑绅士·翔</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
+    <t>钢之咆哮·布瑞恩</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>飓风术</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>泰山之力</t>
+  </si>
+  <si>
+    <t>悟能禅杖</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
     <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>炽阳坠落</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>帝国军魂·莱哈特</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>心灵黑洞1</t>
-  </si>
-  <si>
-    <t>心灵黑洞2</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>黑金勒索者</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>海燕精卫</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>魔卡幻术师·梅基</t>
-  </si>
-  <si>
-    <t>钢之咆哮·布瑞恩</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型1</t>
-  </si>
-  <si>
-    <t>学仆-观测型2</t>
-  </si>
-  <si>
-    <t>沉重否定1</t>
-  </si>
-  <si>
-    <t>沉重否定2</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型2</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>飓风术</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>泰山之力</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
-  </si>
-  <si>
-    <t>传记·钢铁守卫</t>
   </si>
   <si>
     <t>蒙面侠客·翔</t>
@@ -1242,7 +1250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1345,7 +1353,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2">
         <v>22</v>
@@ -1356,10 +1364,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1370,7 +1378,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1378,7 +1386,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
         <v>22</v>
@@ -1392,13 +1400,19 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1406,26 +1420,20 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
-        <f>AVERAGE(C11:C16)</f>
-        <v>21.6666666666667</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="4">
-        <v>3</v>
-      </c>
-      <c r="C22" s="4">
-        <v>22</v>
+      <c r="C20" s="2">
+        <f>AVERAGE(C11:C17)</f>
+        <v>22.2857142857143</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1433,7 +1441,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="4">
         <v>22</v>
@@ -1447,7 +1455,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="4">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1455,10 +1463,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1466,10 +1474,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1477,16 +1485,22 @@
         <v>21</v>
       </c>
       <c r="B27" s="4">
+        <v>6</v>
+      </c>
+      <c r="C27" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="4">
         <v>8</v>
       </c>
-      <c r="C27" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="C28" s="4">
+        <v>21</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="4"/>
@@ -1494,34 +1508,39 @@
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="4">
-        <f>AVERAGE(C22:C27)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C31" s="4">
+        <f>AVERAGE(C23:C28)</f>
+        <v>21.8333333333333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="5">
-        <f>AVERAGE(C2:C5,C11:C16,C22:C27)</f>
-        <v>21.375</v>
+      <c r="B34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="5">
+        <f>AVERAGE(C2:C5,C11:C17,C23:C28)</f>
+        <v>21.9411764705882</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C33 C8" formulaRange="1"/>
+    <ignoredError sqref="C8 C34" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1550,18 +1569,18 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -1572,7 +1591,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1583,7 +1602,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1594,7 +1613,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1605,18 +1624,18 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1627,13 +1646,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1655,13 +1674,13 @@
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>20.625</v>
+        <v>21.125</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -1672,13 +1691,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1696,16 +1715,16 @@
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2">
         <f>AVERAGE(C15:C16)</f>
-        <v>20</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" s="4">
         <v>2</v>
@@ -1716,7 +1735,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" s="4">
         <v>3</v>
@@ -1727,7 +1746,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="4">
         <v>4</v>
@@ -1738,18 +1757,18 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="4">
         <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
@@ -1773,23 +1792,23 @@
         <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C22:C26)</f>
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C9,C15:C16,C22:C26)</f>
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
     </row>
   </sheetData>
@@ -1822,7 +1841,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1833,18 +1852,18 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1855,25 +1874,19 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>22</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1"/>
@@ -1881,59 +1894,65 @@
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>18.2</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>18.5</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -1944,29 +1963,29 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -1977,18 +1996,18 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
       </c>
       <c r="C19" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -2012,22 +2031,22 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2">
-        <f>AVERAGE(C12:C20)</f>
-        <v>17.2222222222222</v>
+        <f>AVERAGE(C11:C20)</f>
+        <v>17.4</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26" s="4">
         <v>5</v>
       </c>
       <c r="C26" s="4">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2045,23 +2064,23 @@
         <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C32" s="5">
-        <f>AVERAGE(C2:C6,C12:C20,C26:C26)</f>
-        <v>17.5333333333333</v>
+        <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
+        <v>17.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2094,7 +2113,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2105,7 +2124,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2116,7 +2135,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2127,7 +2146,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -2138,7 +2157,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2149,7 +2168,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2160,7 +2179,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2171,7 +2190,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2182,7 +2201,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2193,7 +2212,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1">
         <v>4</v>
@@ -2204,7 +2223,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
@@ -2215,7 +2234,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="1">
         <v>4</v>
@@ -2249,7 +2268,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2260,7 +2279,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2">
         <v>4</v>
@@ -2284,7 +2303,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C19:C20)</f>
@@ -2293,7 +2312,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="4">
         <v>4</v>
@@ -2317,7 +2336,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C26:C26)</f>
@@ -2326,10 +2345,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C13,C19:C20,C26:C26)</f>
@@ -2377,7 +2396,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -2388,7 +2407,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -2399,7 +2418,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2410,7 +2429,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2421,7 +2440,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -2432,7 +2451,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2443,7 +2462,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2454,7 +2473,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2465,7 +2484,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -2520,7 +2539,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -2531,7 +2550,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -2542,7 +2561,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -2553,7 +2572,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2">
         <v>3</v>
@@ -2564,7 +2583,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2">
         <v>3</v>
@@ -2575,7 +2594,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2">
         <v>4</v>
@@ -2586,7 +2605,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2">
         <v>4</v>
@@ -2597,7 +2616,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2">
         <v>4</v>
@@ -2622,7 +2641,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2">
         <f>AVERAGE(C18:C26)</f>
@@ -2631,7 +2650,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" s="4">
         <v>2</v>
@@ -2642,7 +2661,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B33" s="4">
         <v>3</v>
@@ -2653,7 +2672,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B34" s="4">
         <v>3</v>
@@ -2664,7 +2683,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B35" s="4">
         <v>4</v>
@@ -2675,7 +2694,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" s="4">
         <v>4</v>
@@ -2686,7 +2705,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="4">
         <v>4</v>
@@ -2697,7 +2716,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" s="4">
         <v>5</v>
@@ -2708,7 +2727,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B39" s="4">
         <v>5</v>
@@ -2719,7 +2738,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B40" s="4">
         <v>6</v>
@@ -2730,7 +2749,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B41" s="4">
         <v>8</v>
@@ -2754,7 +2773,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C44" s="4">
         <f>AVERAGE(C32:C41)</f>
@@ -2763,10 +2782,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C47" s="5">
         <f>AVERAGE(C2:C12,C18:C26,C32:C41)</f>
